--- a/data/Contratos_vigentes_cuadrillas_servicios.xlsx
+++ b/data/Contratos_vigentes_cuadrillas_servicios.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\jmlopez\Desktop\epas-dashboard-v2\epas-dashboard-v2\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{519C99AF-D427-436A-8CEA-3B7FFBBFEB4B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F08ECB6A-1E9F-4B14-BA97-CD3245494DEC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-98" yWindow="-98" windowWidth="19396" windowHeight="11475" xr2:uid="{54D15892-E1DA-4569-BBA0-C690BBE1795B}"/>
+    <workbookView xWindow="-98" yWindow="-98" windowWidth="19396" windowHeight="11475" activeTab="1" xr2:uid="{54D15892-E1DA-4569-BBA0-C690BBE1795B}"/>
   </bookViews>
   <sheets>
     <sheet name="Contratos" sheetId="3" r:id="rId1"/>
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="113" uniqueCount="72">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="118" uniqueCount="76">
   <si>
     <t>BOCAS DE REGISTRO</t>
   </si>
@@ -256,6 +256,18 @@
   </si>
   <si>
     <t>AMPLIACIÓN X 3 MESES - 13-10-2026</t>
+  </si>
+  <si>
+    <t>EX-2026-02252145- -NEU-SECGRAL#EPAS</t>
+  </si>
+  <si>
+    <t>VILLA LA ANGOSTURA</t>
+  </si>
+  <si>
+    <t>OP. Y MANT.PTLC Y SIST. ASOCIADOS</t>
+  </si>
+  <si>
+    <t>4 Op.         1 Tec</t>
   </si>
 </sst>
 </file>
@@ -382,7 +394,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="41">
+  <cellXfs count="43">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -471,18 +483,24 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="1" fillId="2" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="1" fillId="2" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="165" fontId="1" fillId="2" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="165" fontId="1" fillId="2" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -492,11 +510,11 @@
     <xf numFmtId="164" fontId="1" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -830,46 +848,46 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:9" s="6" customFormat="1" x14ac:dyDescent="0.45">
-      <c r="A1" s="33" t="s">
+      <c r="A1" s="34" t="s">
         <v>58</v>
       </c>
-      <c r="B1" s="32" t="s">
+      <c r="B1" s="37" t="s">
         <v>10</v>
       </c>
-      <c r="C1" s="33" t="s">
+      <c r="C1" s="34" t="s">
         <v>11</v>
       </c>
       <c r="D1" s="30"/>
-      <c r="E1" s="33" t="s">
+      <c r="E1" s="34" t="s">
         <v>31</v>
       </c>
-      <c r="F1" s="33" t="s">
+      <c r="F1" s="34" t="s">
         <v>32</v>
       </c>
-      <c r="G1" s="34" t="s">
+      <c r="G1" s="35" t="s">
         <v>55</v>
       </c>
-      <c r="H1" s="35"/>
-      <c r="I1" s="33" t="s">
+      <c r="H1" s="36"/>
+      <c r="I1" s="34" t="s">
         <v>61</v>
       </c>
     </row>
     <row r="2" spans="1:9" s="6" customFormat="1" x14ac:dyDescent="0.45">
-      <c r="A2" s="33"/>
-      <c r="B2" s="32"/>
-      <c r="C2" s="33"/>
+      <c r="A2" s="34"/>
+      <c r="B2" s="37"/>
+      <c r="C2" s="34"/>
       <c r="D2" s="7" t="s">
         <v>38</v>
       </c>
-      <c r="E2" s="33"/>
-      <c r="F2" s="33"/>
+      <c r="E2" s="34"/>
+      <c r="F2" s="34"/>
       <c r="G2" s="16" t="s">
         <v>56</v>
       </c>
       <c r="H2" s="16" t="s">
         <v>57</v>
       </c>
-      <c r="I2" s="33"/>
+      <c r="I2" s="34"/>
     </row>
     <row r="3" spans="1:9" s="3" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A3" s="11" t="s">
@@ -1015,10 +1033,10 @@
       <c r="A8" s="11" t="s">
         <v>59</v>
       </c>
-      <c r="B8" s="39" t="s">
+      <c r="B8" s="32" t="s">
         <v>41</v>
       </c>
-      <c r="C8" s="40" t="s">
+      <c r="C8" s="33" t="s">
         <v>9</v>
       </c>
       <c r="D8" s="8">
@@ -1367,10 +1385,10 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4160B08B-7A96-4C7B-BA3C-78B526366D2A}">
-  <dimension ref="A3:M7"/>
+  <dimension ref="A3:M8"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <cols>
-    <col min="1" max="1" width="10" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="12.19921875" customWidth="1"/>
     <col min="2" max="2" width="17.59765625" customWidth="1"/>
     <col min="3" max="3" width="34.6640625" bestFit="1" customWidth="1"/>
     <col min="4" max="5" width="14.59765625" bestFit="1" customWidth="1"/>
@@ -1385,42 +1403,42 @@
   </cols>
   <sheetData>
     <row r="3" spans="1:13" s="6" customFormat="1" x14ac:dyDescent="0.45">
-      <c r="A3" s="33" t="s">
+      <c r="A3" s="34" t="s">
         <v>58</v>
       </c>
-      <c r="B3" s="32" t="s">
+      <c r="B3" s="37" t="s">
         <v>10</v>
       </c>
-      <c r="C3" s="33" t="s">
+      <c r="C3" s="34" t="s">
         <v>11</v>
       </c>
-      <c r="D3" s="38" t="s">
+      <c r="D3" s="40" t="s">
         <v>29</v>
       </c>
-      <c r="E3" s="38"/>
+      <c r="E3" s="40"/>
       <c r="F3" s="4"/>
-      <c r="G3" s="33" t="s">
+      <c r="G3" s="34" t="s">
         <v>31</v>
       </c>
-      <c r="H3" s="33" t="s">
+      <c r="H3" s="34" t="s">
         <v>32</v>
       </c>
-      <c r="I3" s="33" t="s">
+      <c r="I3" s="34" t="s">
         <v>33</v>
       </c>
-      <c r="J3" s="33" t="s">
+      <c r="J3" s="34" t="s">
         <v>34</v>
       </c>
-      <c r="K3" s="33"/>
-      <c r="L3" s="36" t="s">
+      <c r="K3" s="34"/>
+      <c r="L3" s="38" t="s">
         <v>55</v>
       </c>
-      <c r="M3" s="37"/>
+      <c r="M3" s="39"/>
     </row>
     <row r="4" spans="1:13" s="6" customFormat="1" x14ac:dyDescent="0.45">
-      <c r="A4" s="33"/>
-      <c r="B4" s="32"/>
-      <c r="C4" s="33"/>
+      <c r="A4" s="34"/>
+      <c r="B4" s="37"/>
+      <c r="C4" s="34"/>
       <c r="D4" s="7" t="s">
         <v>30</v>
       </c>
@@ -1430,9 +1448,9 @@
       <c r="F4" s="4" t="s">
         <v>37</v>
       </c>
-      <c r="G4" s="33"/>
-      <c r="H4" s="33"/>
-      <c r="I4" s="33"/>
+      <c r="G4" s="34"/>
+      <c r="H4" s="34"/>
+      <c r="I4" s="34"/>
       <c r="J4" s="4" t="s">
         <v>35</v>
       </c>
@@ -1514,11 +1532,15 @@
       <c r="C7" s="2" t="s">
         <v>70</v>
       </c>
-      <c r="D7" s="8"/>
+      <c r="D7" s="8">
+        <v>614779595.82000005</v>
+      </c>
       <c r="E7" s="8"/>
       <c r="F7" s="2"/>
       <c r="G7" s="1"/>
-      <c r="H7" s="1"/>
+      <c r="H7" s="1">
+        <v>180</v>
+      </c>
       <c r="I7" s="1" t="s">
         <v>69</v>
       </c>
@@ -1530,6 +1552,37 @@
       </c>
       <c r="L7" s="29"/>
       <c r="M7" s="29"/>
+    </row>
+    <row r="8" spans="1:13" ht="28.5" x14ac:dyDescent="0.45">
+      <c r="A8" s="24" t="s">
+        <v>73</v>
+      </c>
+      <c r="B8" s="41" t="s">
+        <v>74</v>
+      </c>
+      <c r="C8" s="42" t="s">
+        <v>72</v>
+      </c>
+      <c r="D8" s="8">
+        <v>402830173.60000002</v>
+      </c>
+      <c r="E8" s="1"/>
+      <c r="F8" s="1"/>
+      <c r="G8" s="1"/>
+      <c r="H8" s="1">
+        <v>180</v>
+      </c>
+      <c r="I8" s="2" t="s">
+        <v>75</v>
+      </c>
+      <c r="J8" s="1" t="s">
+        <v>39</v>
+      </c>
+      <c r="K8" s="1">
+        <v>1</v>
+      </c>
+      <c r="L8" s="1"/>
+      <c r="M8" s="1"/>
     </row>
   </sheetData>
   <mergeCells count="9">
@@ -1544,5 +1597,6 @@
     <mergeCell ref="H3:H4"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
 </worksheet>
 </file>